--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.12919296775595</v>
+        <v>3.433493857260342</v>
       </c>
       <c r="D2" t="n">
-        <v>20.60366643615441</v>
+        <v>3.348095795875092</v>
       </c>
       <c r="E2" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F2" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.44177209170579</v>
+        <v>7.059287964902191</v>
       </c>
       <c r="D3" t="n">
-        <v>42.57271627633484</v>
+        <v>6.918066394904413</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F3" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.76081810513845</v>
+        <v>7.111132942084999</v>
       </c>
       <c r="D4" t="n">
-        <v>43.1123932943982</v>
+        <v>7.005763910339707</v>
       </c>
       <c r="E4" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F4" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.34409057194574</v>
+        <v>7.368414717941183</v>
       </c>
       <c r="D5" t="n">
-        <v>45.29349147965706</v>
+        <v>7.360192365444272</v>
       </c>
       <c r="E5" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F5" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.1644503017487</v>
+        <v>6.039223174034164</v>
       </c>
       <c r="D6" t="n">
-        <v>36.73306938078521</v>
+        <v>5.969123774377596</v>
       </c>
       <c r="E6" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F6" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.9261479707338</v>
+        <v>3.237999045244243</v>
       </c>
       <c r="D7" t="n">
-        <v>19.03864242173548</v>
+        <v>3.093779393532016</v>
       </c>
       <c r="E7" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F7" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.06460597113069</v>
+        <v>3.585498470308738</v>
       </c>
       <c r="D8" t="n">
-        <v>21.27575474521777</v>
+        <v>3.457310146097889</v>
       </c>
       <c r="E8" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F8" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.54072051954979</v>
+        <v>8.21286708442684</v>
       </c>
       <c r="D9" t="n">
-        <v>50.67014833826571</v>
+        <v>8.233899104968179</v>
       </c>
       <c r="E9" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F9" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31694303444191</v>
+        <v>5.251503243096811</v>
       </c>
       <c r="D10" t="n">
-        <v>32.08405151958713</v>
+        <v>5.213658371932908</v>
       </c>
       <c r="E10" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F10" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.686085760521669</v>
+        <v>1.573988936084771</v>
       </c>
       <c r="D11" t="n">
-        <v>10.43686730861766</v>
+        <v>1.69599093765037</v>
       </c>
       <c r="E11" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F11" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.4859133929621</v>
+        <v>6.741460926356342</v>
       </c>
       <c r="D12" t="n">
-        <v>41.97544218086561</v>
+        <v>6.821009354390663</v>
       </c>
       <c r="E12" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F12" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.05637887480304</v>
+        <v>5.534161567155495</v>
       </c>
       <c r="D13" t="n">
-        <v>34.30050961259853</v>
+        <v>5.573832812047262</v>
       </c>
       <c r="E13" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F13" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.26825233490068</v>
+        <v>7.193591004421361</v>
       </c>
       <c r="D14" t="n">
-        <v>45.11217574001498</v>
+        <v>7.330728557752434</v>
       </c>
       <c r="E14" t="n">
-        <v>11.95375866390844</v>
+        <v>1.942485782885121</v>
       </c>
       <c r="F14" t="n">
-        <v>12.02753930061099</v>
+        <v>1.954475136349285</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
